--- a/RMTest-8.xlsx
+++ b/RMTest-8.xlsx
@@ -513,19 +513,19 @@
         <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>4.995</v>
+        <v>4.957</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>4.98</v>
+        <v>5.011</v>
       </c>
       <c r="H2" s="4">
-        <v>0.00154</v>
+        <v>-0.005398</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -539,10 +539,10 @@
         <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>4.995</v>
+        <v>4.957</v>
       </c>
       <c r="E3" s="1">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -559,19 +559,19 @@
         <v>6.25</v>
       </c>
       <c r="D4" s="3">
-        <v>6.244</v>
+        <v>6.169</v>
       </c>
       <c r="E4" s="1">
         <v>49.8</v>
       </c>
       <c r="F4" s="1">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="G4" s="3">
-        <v>6.248</v>
+        <v>6.211</v>
       </c>
       <c r="H4" s="4">
-        <v>-0.000447</v>
+        <v>-0.004184</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -585,19 +585,19 @@
         <v>7.5</v>
       </c>
       <c r="D5" s="3">
-        <v>7.511</v>
+        <v>7.441</v>
       </c>
       <c r="E5" s="1">
-        <v>75.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="F5" s="1">
-        <v>50.3</v>
+        <v>48.8</v>
       </c>
       <c r="G5" s="3">
-        <v>7.526</v>
+        <v>7.468</v>
       </c>
       <c r="H5" s="4">
-        <v>-0.001419</v>
+        <v>-0.002649</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -611,19 +611,19 @@
         <v>8.75</v>
       </c>
       <c r="D6" s="3">
-        <v>8.787000000000001</v>
+        <v>8.722</v>
       </c>
       <c r="E6" s="1">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="F6" s="1">
-        <v>75.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G6" s="3">
-        <v>8.785</v>
+        <v>8.725</v>
       </c>
       <c r="H6" s="4">
-        <v>0.000178</v>
+        <v>-0.000356</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -640,7 +640,7 @@
         <v>9.999000000000001</v>
       </c>
       <c r="E7" s="1">
-        <v>123.9</v>
+        <v>125.1</v>
       </c>
       <c r="F7" s="1">
         <v>99.09999999999999</v>
@@ -649,7 +649,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="4">
-        <v>-0.000114</v>
+        <v>-9.7E-05</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -657,7 +657,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>165.4</v>
+        <v>165.5</v>
       </c>
       <c r="C8" s="2">
         <v>10</v>
@@ -666,10 +666,10 @@
         <v>9.999000000000001</v>
       </c>
       <c r="E8" s="1">
-        <v>165.4</v>
+        <v>165.5</v>
       </c>
       <c r="F8" s="1">
-        <v>140.6</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -683,10 +683,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4.993</v>
+        <v>4.957</v>
       </c>
       <c r="E9" s="1">
-        <v>-25</v>
+        <v>-24.4</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -703,19 +703,19 @@
         <v>3.75</v>
       </c>
       <c r="D10" s="3">
-        <v>3.756</v>
+        <v>3.686</v>
       </c>
       <c r="E10" s="1">
-        <v>-50.3</v>
+        <v>-50.1</v>
       </c>
       <c r="F10" s="1">
-        <v>-25.3</v>
+        <v>-25.7</v>
       </c>
       <c r="G10" s="3">
-        <v>3.698</v>
+        <v>3.718</v>
       </c>
       <c r="H10" s="4">
-        <v>0.005778</v>
+        <v>-0.003282</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -729,19 +729,19 @@
         <v>2.5</v>
       </c>
       <c r="D11" s="3">
-        <v>2.48</v>
+        <v>2.446</v>
       </c>
       <c r="E11" s="1">
         <v>-75.09999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>-50.1</v>
+        <v>-50.7</v>
       </c>
       <c r="G11" s="3">
-        <v>2.443</v>
+        <v>2.457</v>
       </c>
       <c r="H11" s="4">
-        <v>0.003682</v>
+        <v>-0.001093</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -755,19 +755,19 @@
         <v>1.25</v>
       </c>
       <c r="D12" s="3">
-        <v>1.187</v>
+        <v>1.197</v>
       </c>
       <c r="E12" s="1">
-        <v>-100.1</v>
+        <v>-99.90000000000001</v>
       </c>
       <c r="F12" s="1">
-        <v>-75.09999999999999</v>
+        <v>-75.5</v>
       </c>
       <c r="G12" s="3">
-        <v>1.175</v>
+        <v>1.208</v>
       </c>
       <c r="H12" s="4">
-        <v>0.001233</v>
+        <v>-0.001157</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -781,19 +781,19 @@
         <v>0</v>
       </c>
       <c r="D13" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>-123.3</v>
+        <v>-123.9</v>
       </c>
       <c r="F13" s="1">
-        <v>-98.3</v>
+        <v>-99.5</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>6.9E-05</v>
+        <v>1E-05</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -801,7 +801,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="1">
-        <v>-165.4</v>
+        <v>-165.5</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>-165.4</v>
+        <v>-165.5</v>
       </c>
       <c r="F14" s="1">
-        <v>-140.4</v>
+        <v>-141.1</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -821,13 +821,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>49.7</v>
+        <v>50.4</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H16" s="6">
-        <v>0.005778</v>
+        <v>1E-05</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -841,7 +841,7 @@
         <v>26</v>
       </c>
       <c r="H17" s="6">
-        <v>-0.001419</v>
+        <v>-0.005398</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -849,7 +849,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="1">
-        <v>98.3</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -857,7 +857,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="1">
-        <v>197.5</v>
+        <v>198.5</v>
       </c>
     </row>
   </sheetData>
